--- a/Guias/lista_guias1.xlsx
+++ b/Guias/lista_guias1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonzales.c1194\Documents\QAForzaDelivery\Guias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forza\Reposs\ForzaQA_Py_Auto\QAForzaDelivery\Guias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB8E994-0BAD-4E6A-935B-004968405342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24C4C66-6377-4DCC-96ED-7D6FFF7120FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ADAA63C3-DEED-40C5-8E23-B251FDE6385C}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="18080" windowHeight="9500" xr2:uid="{ADAA63C3-DEED-40C5-8E23-B251FDE6385C}"/>
   </bookViews>
   <sheets>
     <sheet name="Guias" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -159,7 +159,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -265,7 +265,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -407,7 +407,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -416,57 +416,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{276E24EB-9E78-4C88-B311-7CCFABE133E5}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
